--- a/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
@@ -757,13 +757,13 @@
         <v>0.44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         <v>0.22</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         <v>0.28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         <v>0.28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
@@ -1389,13 +1389,13 @@
         <v>0.375</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         <v>0.375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         <v>0.4375</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
@@ -1868,13 +1868,13 @@
         <v>0.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         <v>0.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -2189,13 +2189,13 @@
         <v>0.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
@@ -2352,13 +2352,13 @@
         <v>0.656</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.37874</v>
+        <v>0.37824</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.37874</v>
+        <v>0.37824</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.75748</v>
+        <v>0.75698</v>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
         <v>0.655</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>0.655</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -2841,13 +2841,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
@@ -3004,13 +3004,13 @@
         <v>0.9375</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
@@ -3167,13 +3167,13 @@
         <v>1.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
@@ -792,12 +792,17 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.47~1.470; N2@DRIVE=1.47~1.470; Y@REF=0.88~0.875; D1@BORE=0.53~0.531; D2@BORE=0.53~0.531</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -813,7 +818,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="C3" t="n">
         <v>0.22</v>
@@ -831,7 +836,7 @@
         <v>0.1161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="I3" t="n">
         <v>0.22</v>
@@ -852,13 +857,13 @@
         <v>0.19</v>
       </c>
       <c r="O3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="P3" t="n">
         <v>0.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
         <v>0.39314</v>
@@ -876,7 +881,7 @@
         <v>0.16694</v>
       </c>
       <c r="W3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="X3" t="n">
         <v>0.39314</v>
@@ -894,19 +899,19 @@
         <v>0.16694</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="AD3" t="n">
         <v>0.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="AF3" t="n">
         <v>0.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="AH3" t="n">
         <v>0.22</v>
@@ -955,7 +960,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100)</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1108,12 +1118,17 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.09~1.090; N2@DRIVE=0.9~0.900; Y@REF=0.56~0.562; D1@BORE=0.28~0.281; D2@BORE=0.19~0.188</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1266,12 +1281,17 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.09~1.090; N2@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.28~0.281; D2@BORE=0.28~0.281</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1424,12 +1444,17 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.22~1.220; N2@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.41~0.406; D2@BORE=0.28~0.281</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1582,12 +1607,17 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.22~1.220; N2@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.41~0.406; D2@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1903,12 +1933,17 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>Air-Way s127 only (double-pass 29 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.47~1.470; N2@DRIVE=1.28~1.280; Y@REF=0.88~0.875; D1@BORE=0.53~0.531; D2@BORE=0.41~0.406</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2061,7 +2096,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2071,7 +2106,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.59~1.590; N2@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.72~0.719; D2@BORE=0.53~0.531 | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -2224,7 +2259,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2234,7 +2269,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.59~1.590; N2@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.72~0.719; D2@BORE=0.72~0.719 | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2713,7 +2748,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2723,7 +2758,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.97~1.970; N2@DRIVE=1.97~1.970; Y@REF=1.31~1.312; D1@BORE=0.94~0.938; D2@BORE=0.94~0.938 | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2876,7 +2911,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2886,7 +2921,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>A(2) printed "1 1/2-11 1/2" both passes (a -20 end is 1 1/4-11 1/2; D2=1.25 supports 1 1/4) - as-printed, likely typo | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A(2) printed "1 1/2-11 1/2" both passes (a -20 end is 1 1/4-11 1/2; D2=1.25 supports 1 1/4) - as-printed, likely typo | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=2.38~2.380; N2@DRIVE=2.38~2.380; Y@REF=1.63~1.625; D1@BORE=1.25~1.250; D2@BORE=1.25~1.250 | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5500_SW2.xlsx
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="C3" t="n">
         <v>0.22</v>
@@ -836,7 +836,7 @@
         <v>0.1161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="n">
         <v>0.22</v>
@@ -857,13 +857,13 @@
         <v>0.19</v>
       </c>
       <c r="O3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="P3" t="n">
         <v>0.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="R3" t="n">
         <v>0.39314</v>
@@ -881,7 +881,7 @@
         <v>0.16694</v>
       </c>
       <c r="W3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="X3" t="n">
         <v>0.39314</v>
@@ -899,19 +899,19 @@
         <v>0.16694</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AD3" t="n">
         <v>0.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="AF3" t="n">
         <v>0.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="AH3" t="n">
         <v>0.22</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 0.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; N2@DRIVE: Air-Way 0.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.72 | 2026-10-20 Air-Way first: N2@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -3103,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="D17" t="n">
         <v>1.16929</v>
@@ -3121,7 +3121,7 @@
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="J17" t="n">
         <v>1.16929</v>
@@ -3184,31 +3184,31 @@
         <v>3</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AE17" t="n">
         <v>1.97</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AG17" t="n">
         <v>1.97</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.72119</v>
+        <v>0.7442800000000001</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.72119</v>
+        <v>0.7442800000000001</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.44288</v>
+        <v>1.48906</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3242,7 +3242,12 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1448 Hex Flat = 2.500 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s127 only (double-pass 29 rows); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1448 Hex Flat = 2.500 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: Y@REF OMi/Brennan 2.5 -&gt; Air-Way 2.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
